--- a/model/basket-economics.xlsx
+++ b/model/basket-economics.xlsx
@@ -7,11 +7,12 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Inputs" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Calc" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Sensitivity" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Chart" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Notes" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Summary" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Inputs" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Calc" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Sensitivity" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Chart" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Notes" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -28,7 +29,7 @@
     <numFmt numFmtId="168" formatCode="0.00x"/>
     <numFmt numFmtId="169" formatCode="+0.0%;-0.0%"/>
   </numFmts>
-  <fonts count="13">
+  <fonts count="17">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -62,11 +63,16 @@
     <font>
       <name val="Calibri"/>
       <b val="1"/>
-      <color rgb="008A6D00"/>
+      <color rgb="000000C0"/>
       <sz val="11"/>
     </font>
     <font>
       <b val="1"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <color rgb="00007B3A"/>
+      <sz val="11"/>
     </font>
     <font>
       <b val="1"/>
@@ -87,6 +93,24 @@
     <font>
       <i val="1"/>
       <color rgb="002E6DB4"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="001F2A44"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="002E6DB4"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="00007B3A"/>
+      <sz val="11"/>
     </font>
     <font>
       <b val="1"/>
@@ -121,7 +145,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="7">
     <border>
       <left/>
       <right/>
@@ -143,11 +167,69 @@
         <color rgb="00BFC7D5"/>
       </bottom>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="00BFC7D5"/>
+      </left>
+      <right style="thin">
+        <color rgb="00BFC7D5"/>
+      </right>
+      <top style="thin">
+        <color rgb="00BFC7D5"/>
+      </top>
+      <bottom style="double">
+        <color rgb="001F2A44"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00BFC7D5"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00BFC7D5"/>
+      </right>
+      <top style="thin">
+        <color rgb="00BFC7D5"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00BFC7D5"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00BFC7D5"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00BFC7D5"/>
+      </right>
+      <top style="thin">
+        <color rgb="00BFC7D5"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00BFC7D5"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="40">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -156,6 +238,26 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="15" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="15" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="15" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="15" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -170,24 +272,23 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="10" fontId="6" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="10" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="7" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="10" fontId="7" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="8" fillId="5" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="167" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="168" fontId="5" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="7" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="169" fontId="11" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="169" fontId="12" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -270,6 +371,102 @@
 </file>
 
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <style val="10"/>
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t>Basket value / tonne REO by scenario (illustrative)</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <barChart>
+        <barDir val="col"/>
+        <grouping val="clustered"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>'Summary'!B22</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Summary'!$A$23:$A$25</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Summary'!$B$23:$B$25</f>
+            </numRef>
+          </val>
+        </ser>
+        <gapWidth val="150"/>
+        <axId val="10"/>
+        <axId val="100"/>
+      </barChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>USD / tonne</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <numFmt formatCode="&quot;$&quot;#,##0" sourceLinked="0"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
 <chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <style val="10"/>
   <chart>
@@ -380,6 +577,33 @@
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>5</col>
+      <colOff>0</colOff>
+      <row>12</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="5760000" cy="3240000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="1" name="Chart 1"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
 <wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
@@ -695,6 +919,278 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:E25"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="40" customWidth="1" min="1" max="1"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="8" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="4" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="26" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>THE 17 — BASKET-ECONOMICS MODEL</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="2" t="n"/>
+      <c r="D1" s="2" t="n"/>
+      <c r="E1" s="2" t="n"/>
+    </row>
+    <row r="2" ht="28" customHeight="1">
+      <c r="A2" s="3" t="inlineStr">
+        <is>
+          <t>Rare-earth basket value per tonne of mixed REO, with price-floor and export-control-shock scenarios. Prepared 2026-07-07. ALL FIGURES ILLUSTRATIVE until Inputs are replaced with real data — see Notes tab.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>TABLE OF CONTENTS</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>Summary</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="inlineStr">
+        <is>
+          <t>This dashboard — key outputs &amp; sensitivity chart.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>Inputs</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="inlineStr">
+        <is>
+          <t>Deposit % by oxide + oxide prices. BLUE cells = hardcoded inputs to replace.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>Calc</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="inlineStr">
+        <is>
+          <t>Weighted basket value / tonne REO; % contribution by element.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>Sensitivity</t>
+        </is>
+      </c>
+      <c r="B8" s="6" t="inlineStr">
+        <is>
+          <t>Price-floor &amp; export-control-shock scenarios.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>Chart</t>
+        </is>
+      </c>
+      <c r="B9" s="6" t="inlineStr">
+        <is>
+          <t>% contribution to basket value by element.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+      <c r="B10" s="6" t="inlineStr">
+        <is>
+          <t>Read me — conventions, caveats, fill-in checklist.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>KEY OUTPUTS</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="7" t="inlineStr">
+        <is>
+          <t>Basket value / tonne REO (base)</t>
+        </is>
+      </c>
+      <c r="B14" s="8" t="n"/>
+      <c r="C14" s="8" t="n"/>
+      <c r="D14" s="9">
+        <f>Calc!F21</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="7" t="inlineStr">
+        <is>
+          <t>Basket value / tonne (price-floor scenario)</t>
+        </is>
+      </c>
+      <c r="B15" s="8" t="n"/>
+      <c r="C15" s="8" t="n"/>
+      <c r="D15" s="10">
+        <f>Sensitivity!D26</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="7" t="inlineStr">
+        <is>
+          <t>Basket value / tonne (export-control shock)</t>
+        </is>
+      </c>
+      <c r="B16" s="8" t="n"/>
+      <c r="C16" s="8" t="n"/>
+      <c r="D16" s="10">
+        <f>Sensitivity!E26</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="7" t="inlineStr">
+        <is>
+          <t>Uplift vs base — floor</t>
+        </is>
+      </c>
+      <c r="B17" s="8" t="n"/>
+      <c r="C17" s="8" t="n"/>
+      <c r="D17" s="11">
+        <f>Sensitivity!D27</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="7" t="inlineStr">
+        <is>
+          <t>Uplift vs base — shock</t>
+        </is>
+      </c>
+      <c r="B18" s="8" t="n"/>
+      <c r="C18" s="8" t="n"/>
+      <c r="D18" s="11">
+        <f>Sensitivity!E27</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="7" t="inlineStr">
+        <is>
+          <t>Magnet elements (NdPr+Dy+Tb) share of basket value</t>
+        </is>
+      </c>
+      <c r="B19" s="8" t="n"/>
+      <c r="C19" s="8" t="n"/>
+      <c r="D19" s="12">
+        <f>Calc!F23</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="6" t="inlineStr">
+        <is>
+          <t>Green = pulled live from other tabs. Headline row double-underlined. Figures illustrative until Inputs are real.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="13" t="inlineStr">
+        <is>
+          <t>Scenario</t>
+        </is>
+      </c>
+      <c r="B22" s="13" t="inlineStr">
+        <is>
+          <t>Basket value USD/tonne</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="14" t="inlineStr">
+        <is>
+          <t>Base</t>
+        </is>
+      </c>
+      <c r="B23" s="15">
+        <f>Calc!F21</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="14" t="inlineStr">
+        <is>
+          <t>Price floor</t>
+        </is>
+      </c>
+      <c r="B24" s="15">
+        <f>Sensitivity!D26</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="14" t="inlineStr">
+        <is>
+          <t>Export-control shock</t>
+        </is>
+      </c>
+      <c r="B25" s="15">
+        <f>Sensitivity!E26</f>
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="14">
+    <mergeCell ref="B9:E9"/>
+    <mergeCell ref="A19:C19"/>
+    <mergeCell ref="B8:E8"/>
+    <mergeCell ref="A2:E2"/>
+    <mergeCell ref="A14:C14"/>
+    <mergeCell ref="B6:E6"/>
+    <mergeCell ref="A17:C17"/>
+    <mergeCell ref="A18:C18"/>
+    <mergeCell ref="B7:E7"/>
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="B5:E5"/>
+    <mergeCell ref="A15:C15"/>
+    <mergeCell ref="B10:E10"/>
+    <mergeCell ref="A16:C16"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:G21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -728,531 +1224,531 @@
       </c>
     </row>
     <row r="3" ht="42" customHeight="1">
-      <c r="A3" s="4" t="inlineStr">
+      <c r="A3" s="16" t="inlineStr">
         <is>
           <t>Element</t>
         </is>
       </c>
-      <c r="B3" s="4" t="inlineStr">
+      <c r="B3" s="16" t="inlineStr">
         <is>
           <t>Oxide</t>
         </is>
       </c>
-      <c r="C3" s="4" t="inlineStr">
+      <c r="C3" s="16" t="inlineStr">
         <is>
           <t>Group</t>
         </is>
       </c>
-      <c r="D3" s="4" t="inlineStr">
+      <c r="D3" s="16" t="inlineStr">
         <is>
           <t>Example Deposit A
 (% by oxide) [[INPUT]]</t>
         </is>
       </c>
-      <c r="E3" s="4" t="inlineStr">
+      <c r="E3" s="16" t="inlineStr">
         <is>
           <t>Example Deposit B
 (% by oxide) [[INPUT]]</t>
         </is>
       </c>
-      <c r="F3" s="4" t="inlineStr">
+      <c r="F3" s="16" t="inlineStr">
         <is>
           <t>Oxide price
 (USD/kg) [[VERIFY: as of &lt;date&gt;]]</t>
         </is>
       </c>
-      <c r="G3" s="4" t="inlineStr">
+      <c r="G3" s="16" t="inlineStr">
         <is>
           <t>Magnet element?</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="5" t="inlineStr">
+      <c r="A4" s="17" t="inlineStr">
         <is>
           <t>Lanthanum (La)</t>
         </is>
       </c>
-      <c r="B4" s="5" t="inlineStr">
+      <c r="B4" s="17" t="inlineStr">
         <is>
           <t>La2O3</t>
         </is>
       </c>
-      <c r="C4" s="5" t="inlineStr">
+      <c r="C4" s="17" t="inlineStr">
         <is>
           <t>Light</t>
         </is>
       </c>
-      <c r="D4" s="6" t="n">
+      <c r="D4" s="18" t="n">
         <v>0.28</v>
       </c>
-      <c r="E4" s="6" t="n">
+      <c r="E4" s="18" t="n">
         <v>0.22</v>
       </c>
-      <c r="F4" s="7" t="n">
+      <c r="F4" s="19" t="n">
         <v>1</v>
       </c>
-      <c r="G4" s="5" t="inlineStr"/>
+      <c r="G4" s="17" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="5" t="inlineStr">
+      <c r="A5" s="17" t="inlineStr">
         <is>
           <t>Cerium (Ce)</t>
         </is>
       </c>
-      <c r="B5" s="5" t="inlineStr">
+      <c r="B5" s="17" t="inlineStr">
         <is>
           <t>CeO2</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="C5" s="17" t="inlineStr">
         <is>
           <t>Light</t>
         </is>
       </c>
-      <c r="D5" s="6" t="n">
+      <c r="D5" s="18" t="n">
         <v>0.45</v>
       </c>
-      <c r="E5" s="6" t="n">
+      <c r="E5" s="18" t="n">
         <v>0.4</v>
       </c>
-      <c r="F5" s="7" t="n">
+      <c r="F5" s="19" t="n">
         <v>1</v>
       </c>
-      <c r="G5" s="5" t="inlineStr"/>
+      <c r="G5" s="17" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="5" t="inlineStr">
+      <c r="A6" s="17" t="inlineStr">
         <is>
           <t>Praseodymium (Pr)</t>
         </is>
       </c>
-      <c r="B6" s="5" t="inlineStr">
+      <c r="B6" s="17" t="inlineStr">
         <is>
           <t>Pr6O11</t>
         </is>
       </c>
-      <c r="C6" s="5" t="inlineStr">
+      <c r="C6" s="17" t="inlineStr">
         <is>
           <t>Light (magnet)</t>
         </is>
       </c>
-      <c r="D6" s="6" t="n">
+      <c r="D6" s="18" t="n">
         <v>0.045</v>
       </c>
-      <c r="E6" s="6" t="n">
+      <c r="E6" s="18" t="n">
         <v>0.04</v>
       </c>
-      <c r="F6" s="7" t="n">
+      <c r="F6" s="19" t="n">
         <v>90</v>
       </c>
-      <c r="G6" s="5" t="inlineStr">
+      <c r="G6" s="17" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="5" t="inlineStr">
+      <c r="A7" s="17" t="inlineStr">
         <is>
           <t>Neodymium (Nd)</t>
         </is>
       </c>
-      <c r="B7" s="5" t="inlineStr">
+      <c r="B7" s="17" t="inlineStr">
         <is>
           <t>Nd2O3</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr">
+      <c r="C7" s="17" t="inlineStr">
         <is>
           <t>Light (magnet)</t>
         </is>
       </c>
-      <c r="D7" s="6" t="n">
+      <c r="D7" s="18" t="n">
         <v>0.16</v>
       </c>
-      <c r="E7" s="6" t="n">
+      <c r="E7" s="18" t="n">
         <v>0.14</v>
       </c>
-      <c r="F7" s="7" t="n">
+      <c r="F7" s="19" t="n">
         <v>90</v>
       </c>
-      <c r="G7" s="5" t="inlineStr">
+      <c r="G7" s="17" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="5" t="inlineStr">
+      <c r="A8" s="17" t="inlineStr">
         <is>
           <t>Samarium (Sm)</t>
         </is>
       </c>
-      <c r="B8" s="5" t="inlineStr">
+      <c r="B8" s="17" t="inlineStr">
         <is>
           <t>Sm2O3</t>
         </is>
       </c>
-      <c r="C8" s="5" t="inlineStr">
+      <c r="C8" s="17" t="inlineStr">
         <is>
           <t>Light</t>
         </is>
       </c>
-      <c r="D8" s="6" t="n">
+      <c r="D8" s="18" t="n">
         <v>0.02</v>
       </c>
-      <c r="E8" s="6" t="n">
+      <c r="E8" s="18" t="n">
         <v>0.025</v>
       </c>
-      <c r="F8" s="7" t="n">
+      <c r="F8" s="19" t="n">
         <v>3</v>
       </c>
-      <c r="G8" s="5" t="inlineStr"/>
+      <c r="G8" s="17" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="5" t="inlineStr">
+      <c r="A9" s="17" t="inlineStr">
         <is>
           <t>Europium (Eu)</t>
         </is>
       </c>
-      <c r="B9" s="5" t="inlineStr">
+      <c r="B9" s="17" t="inlineStr">
         <is>
           <t>Eu2O3</t>
         </is>
       </c>
-      <c r="C9" s="5" t="inlineStr">
+      <c r="C9" s="17" t="inlineStr">
         <is>
           <t>Heavy</t>
         </is>
       </c>
-      <c r="D9" s="6" t="n">
+      <c r="D9" s="18" t="n">
         <v>0.003</v>
       </c>
-      <c r="E9" s="6" t="n">
+      <c r="E9" s="18" t="n">
         <v>0.004</v>
       </c>
-      <c r="F9" s="7" t="n">
+      <c r="F9" s="19" t="n">
         <v>28</v>
       </c>
-      <c r="G9" s="5" t="inlineStr"/>
+      <c r="G9" s="17" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="5" t="inlineStr">
+      <c r="A10" s="17" t="inlineStr">
         <is>
           <t>Gadolinium (Gd)</t>
         </is>
       </c>
-      <c r="B10" s="5" t="inlineStr">
+      <c r="B10" s="17" t="inlineStr">
         <is>
           <t>Gd2O3</t>
         </is>
       </c>
-      <c r="C10" s="5" t="inlineStr">
+      <c r="C10" s="17" t="inlineStr">
         <is>
           <t>Heavy</t>
         </is>
       </c>
-      <c r="D10" s="6" t="n">
+      <c r="D10" s="18" t="n">
         <v>0.012</v>
       </c>
-      <c r="E10" s="6" t="n">
+      <c r="E10" s="18" t="n">
         <v>0.02</v>
       </c>
-      <c r="F10" s="7" t="n">
+      <c r="F10" s="19" t="n">
         <v>30</v>
       </c>
-      <c r="G10" s="5" t="inlineStr"/>
+      <c r="G10" s="17" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="5" t="inlineStr">
+      <c r="A11" s="17" t="inlineStr">
         <is>
           <t>Terbium (Tb)</t>
         </is>
       </c>
-      <c r="B11" s="5" t="inlineStr">
+      <c r="B11" s="17" t="inlineStr">
         <is>
           <t>Tb4O7</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr">
+      <c r="C11" s="17" t="inlineStr">
         <is>
           <t>Heavy (magnet)</t>
         </is>
       </c>
-      <c r="D11" s="6" t="n">
+      <c r="D11" s="18" t="n">
         <v>0.002</v>
       </c>
-      <c r="E11" s="6" t="n">
+      <c r="E11" s="18" t="n">
         <v>0.015</v>
       </c>
-      <c r="F11" s="7" t="n">
+      <c r="F11" s="19" t="n">
         <v>900</v>
       </c>
-      <c r="G11" s="5" t="inlineStr">
+      <c r="G11" s="17" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="5" t="inlineStr">
+      <c r="A12" s="17" t="inlineStr">
         <is>
           <t>Dysprosium (Dy)</t>
         </is>
       </c>
-      <c r="B12" s="5" t="inlineStr">
+      <c r="B12" s="17" t="inlineStr">
         <is>
           <t>Dy2O3</t>
         </is>
       </c>
-      <c r="C12" s="5" t="inlineStr">
+      <c r="C12" s="17" t="inlineStr">
         <is>
           <t>Heavy (magnet)</t>
         </is>
       </c>
-      <c r="D12" s="6" t="n">
+      <c r="D12" s="18" t="n">
         <v>0.01</v>
       </c>
-      <c r="E12" s="6" t="n">
+      <c r="E12" s="18" t="n">
         <v>0.06</v>
       </c>
-      <c r="F12" s="7" t="n">
+      <c r="F12" s="19" t="n">
         <v>350</v>
       </c>
-      <c r="G12" s="5" t="inlineStr">
+      <c r="G12" s="17" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="5" t="inlineStr">
+      <c r="A13" s="17" t="inlineStr">
         <is>
           <t>Holmium (Ho)</t>
         </is>
       </c>
-      <c r="B13" s="5" t="inlineStr">
+      <c r="B13" s="17" t="inlineStr">
         <is>
           <t>Ho2O3</t>
         </is>
       </c>
-      <c r="C13" s="5" t="inlineStr">
+      <c r="C13" s="17" t="inlineStr">
         <is>
           <t>Heavy</t>
         </is>
       </c>
-      <c r="D13" s="6" t="n">
+      <c r="D13" s="18" t="n">
         <v>0.0015</v>
       </c>
-      <c r="E13" s="6" t="n">
+      <c r="E13" s="18" t="n">
         <v>0.008</v>
       </c>
-      <c r="F13" s="7" t="n">
+      <c r="F13" s="19" t="n">
         <v>90</v>
       </c>
-      <c r="G13" s="5" t="inlineStr"/>
+      <c r="G13" s="17" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="5" t="inlineStr">
+      <c r="A14" s="17" t="inlineStr">
         <is>
           <t>Erbium (Er)</t>
         </is>
       </c>
-      <c r="B14" s="5" t="inlineStr">
+      <c r="B14" s="17" t="inlineStr">
         <is>
           <t>Er2O3</t>
         </is>
       </c>
-      <c r="C14" s="5" t="inlineStr">
+      <c r="C14" s="17" t="inlineStr">
         <is>
           <t>Heavy</t>
         </is>
       </c>
-      <c r="D14" s="6" t="n">
+      <c r="D14" s="18" t="n">
         <v>0.004</v>
       </c>
-      <c r="E14" s="6" t="n">
+      <c r="E14" s="18" t="n">
         <v>0.025</v>
       </c>
-      <c r="F14" s="7" t="n">
+      <c r="F14" s="19" t="n">
         <v>30</v>
       </c>
-      <c r="G14" s="5" t="inlineStr"/>
+      <c r="G14" s="17" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="5" t="inlineStr">
+      <c r="A15" s="17" t="inlineStr">
         <is>
           <t>Thulium (Tm)</t>
         </is>
       </c>
-      <c r="B15" s="5" t="inlineStr">
+      <c r="B15" s="17" t="inlineStr">
         <is>
           <t>Tm2O3</t>
         </is>
       </c>
-      <c r="C15" s="5" t="inlineStr">
+      <c r="C15" s="17" t="inlineStr">
         <is>
           <t>Heavy</t>
         </is>
       </c>
-      <c r="D15" s="6" t="n">
+      <c r="D15" s="18" t="n">
         <v>0.0005</v>
       </c>
-      <c r="E15" s="6" t="n">
+      <c r="E15" s="18" t="n">
         <v>0.003</v>
       </c>
-      <c r="F15" s="7" t="n">
+      <c r="F15" s="19" t="n">
         <v>100</v>
       </c>
-      <c r="G15" s="5" t="inlineStr"/>
+      <c r="G15" s="17" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="5" t="inlineStr">
+      <c r="A16" s="17" t="inlineStr">
         <is>
           <t>Ytterbium (Yb)</t>
         </is>
       </c>
-      <c r="B16" s="5" t="inlineStr">
+      <c r="B16" s="17" t="inlineStr">
         <is>
           <t>Yb2O3</t>
         </is>
       </c>
-      <c r="C16" s="5" t="inlineStr">
+      <c r="C16" s="17" t="inlineStr">
         <is>
           <t>Heavy</t>
         </is>
       </c>
-      <c r="D16" s="6" t="n">
+      <c r="D16" s="18" t="n">
         <v>0.002</v>
       </c>
-      <c r="E16" s="6" t="n">
+      <c r="E16" s="18" t="n">
         <v>0.015</v>
       </c>
-      <c r="F16" s="7" t="n">
+      <c r="F16" s="19" t="n">
         <v>18</v>
       </c>
-      <c r="G16" s="5" t="inlineStr"/>
+      <c r="G16" s="17" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="5" t="inlineStr">
+      <c r="A17" s="17" t="inlineStr">
         <is>
           <t>Lutetium (Lu)</t>
         </is>
       </c>
-      <c r="B17" s="5" t="inlineStr">
+      <c r="B17" s="17" t="inlineStr">
         <is>
           <t>Lu2O3</t>
         </is>
       </c>
-      <c r="C17" s="5" t="inlineStr">
+      <c r="C17" s="17" t="inlineStr">
         <is>
           <t>Heavy</t>
         </is>
       </c>
-      <c r="D17" s="6" t="n">
+      <c r="D17" s="18" t="n">
         <v>0.0005</v>
       </c>
-      <c r="E17" s="6" t="n">
+      <c r="E17" s="18" t="n">
         <v>0.003</v>
       </c>
-      <c r="F17" s="7" t="n">
+      <c r="F17" s="19" t="n">
         <v>600</v>
       </c>
-      <c r="G17" s="5" t="inlineStr"/>
+      <c r="G17" s="17" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="5" t="inlineStr">
+      <c r="A18" s="17" t="inlineStr">
         <is>
           <t>Yttrium (Y)</t>
         </is>
       </c>
-      <c r="B18" s="5" t="inlineStr">
+      <c r="B18" s="17" t="inlineStr">
         <is>
           <t>Y2O3</t>
         </is>
       </c>
-      <c r="C18" s="5" t="inlineStr">
+      <c r="C18" s="17" t="inlineStr">
         <is>
           <t>Heavy</t>
         </is>
       </c>
-      <c r="D18" s="6" t="n">
+      <c r="D18" s="18" t="n">
         <v>0.006999999999999999</v>
       </c>
-      <c r="E18" s="6" t="n">
+      <c r="E18" s="18" t="n">
         <v>0.015</v>
       </c>
-      <c r="F18" s="7" t="n">
+      <c r="F18" s="19" t="n">
         <v>8</v>
       </c>
-      <c r="G18" s="5" t="inlineStr"/>
+      <c r="G18" s="17" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="5" t="inlineStr">
+      <c r="A19" s="17" t="inlineStr">
         <is>
           <t>Scandium (Sc)</t>
         </is>
       </c>
-      <c r="B19" s="5" t="inlineStr">
+      <c r="B19" s="17" t="inlineStr">
         <is>
           <t>Sc2O3</t>
         </is>
       </c>
-      <c r="C19" s="5" t="inlineStr">
+      <c r="C19" s="17" t="inlineStr">
         <is>
           <t>Heavy</t>
         </is>
       </c>
-      <c r="D19" s="6" t="n">
+      <c r="D19" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="E19" s="6" t="n">
+      <c r="E19" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="F19" s="7" t="n">
+      <c r="F19" s="19" t="n">
         <v>1000</v>
       </c>
-      <c r="G19" s="5" t="inlineStr"/>
+      <c r="G19" s="17" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="5" t="inlineStr">
+      <c r="A20" s="17" t="inlineStr">
         <is>
           <t>Promethium (Pm)</t>
         </is>
       </c>
-      <c r="B20" s="5" t="inlineStr">
+      <c r="B20" s="17" t="inlineStr">
         <is>
           <t>Pm2O3</t>
         </is>
       </c>
-      <c r="C20" s="5" t="inlineStr">
+      <c r="C20" s="17" t="inlineStr">
         <is>
           <t>n/a</t>
         </is>
       </c>
-      <c r="D20" s="6" t="n">
+      <c r="D20" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="E20" s="6" t="n">
+      <c r="E20" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="F20" s="7" t="n">
+      <c r="F20" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="G20" s="5" t="inlineStr"/>
+      <c r="G20" s="17" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="C21" s="8" t="inlineStr">
+      <c r="C21" s="20" t="inlineStr">
         <is>
           <t>TOTAL (should be ~100%)</t>
         </is>
       </c>
-      <c r="D21" s="9">
+      <c r="D21" s="21">
         <f>SUM(D4:D20)</f>
         <v/>
       </c>
-      <c r="E21" s="9">
+      <c r="E21" s="21">
         <f>SUM(E4:E20)</f>
         <v/>
       </c>
@@ -1266,7 +1762,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1307,643 +1803,643 @@
       </c>
     </row>
     <row r="3" ht="30" customHeight="1">
-      <c r="A3" s="4" t="inlineStr">
+      <c r="A3" s="16" t="inlineStr">
         <is>
           <t>Element</t>
         </is>
       </c>
-      <c r="B3" s="4" t="inlineStr">
+      <c r="B3" s="16" t="inlineStr">
         <is>
           <t>Group</t>
         </is>
       </c>
-      <c r="C3" s="4" t="inlineStr">
+      <c r="C3" s="16" t="inlineStr">
         <is>
           <t>% by oxide (A)</t>
         </is>
       </c>
-      <c r="D3" s="4" t="inlineStr">
+      <c r="D3" s="16" t="inlineStr">
         <is>
           <t>Price USD/kg</t>
         </is>
       </c>
-      <c r="E3" s="4" t="inlineStr">
+      <c r="E3" s="16" t="inlineStr">
         <is>
           <t>kg per tonne REO</t>
         </is>
       </c>
-      <c r="F3" s="4" t="inlineStr">
+      <c r="F3" s="16" t="inlineStr">
         <is>
           <t>Value USD/tonne</t>
         </is>
       </c>
-      <c r="G3" s="4" t="inlineStr">
+      <c r="G3" s="16" t="inlineStr">
         <is>
           <t>% of basket value</t>
         </is>
       </c>
-      <c r="H3" s="4" t="inlineStr">
+      <c r="H3" s="16" t="inlineStr">
         <is>
           <t>Magnet element?</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="10">
+      <c r="A4" s="22">
         <f>Inputs!A4</f>
         <v/>
       </c>
-      <c r="B4" s="10">
+      <c r="B4" s="22">
         <f>Inputs!C4</f>
         <v/>
       </c>
-      <c r="C4" s="11">
+      <c r="C4" s="23">
         <f>Inputs!D4</f>
         <v/>
       </c>
-      <c r="D4" s="12">
+      <c r="D4" s="24">
         <f>Inputs!F4</f>
         <v/>
       </c>
-      <c r="E4" s="13">
+      <c r="E4" s="25">
         <f>C4*1000</f>
         <v/>
       </c>
-      <c r="F4" s="14">
+      <c r="F4" s="26">
         <f>E4*D4</f>
         <v/>
       </c>
-      <c r="G4" s="15">
+      <c r="G4" s="27">
         <f>F4/$F$21</f>
         <v/>
       </c>
-      <c r="H4" s="10">
+      <c r="H4" s="22">
         <f>Inputs!G4</f>
         <v/>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="10">
+      <c r="A5" s="22">
         <f>Inputs!A5</f>
         <v/>
       </c>
-      <c r="B5" s="10">
+      <c r="B5" s="22">
         <f>Inputs!C5</f>
         <v/>
       </c>
-      <c r="C5" s="11">
+      <c r="C5" s="23">
         <f>Inputs!D5</f>
         <v/>
       </c>
-      <c r="D5" s="12">
+      <c r="D5" s="24">
         <f>Inputs!F5</f>
         <v/>
       </c>
-      <c r="E5" s="13">
+      <c r="E5" s="25">
         <f>C5*1000</f>
         <v/>
       </c>
-      <c r="F5" s="14">
+      <c r="F5" s="26">
         <f>E5*D5</f>
         <v/>
       </c>
-      <c r="G5" s="15">
+      <c r="G5" s="27">
         <f>F5/$F$21</f>
         <v/>
       </c>
-      <c r="H5" s="10">
+      <c r="H5" s="22">
         <f>Inputs!G5</f>
         <v/>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="10">
+      <c r="A6" s="22">
         <f>Inputs!A6</f>
         <v/>
       </c>
-      <c r="B6" s="10">
+      <c r="B6" s="22">
         <f>Inputs!C6</f>
         <v/>
       </c>
-      <c r="C6" s="11">
+      <c r="C6" s="23">
         <f>Inputs!D6</f>
         <v/>
       </c>
-      <c r="D6" s="12">
+      <c r="D6" s="24">
         <f>Inputs!F6</f>
         <v/>
       </c>
-      <c r="E6" s="13">
+      <c r="E6" s="25">
         <f>C6*1000</f>
         <v/>
       </c>
-      <c r="F6" s="14">
+      <c r="F6" s="26">
         <f>E6*D6</f>
         <v/>
       </c>
-      <c r="G6" s="15">
+      <c r="G6" s="27">
         <f>F6/$F$21</f>
         <v/>
       </c>
-      <c r="H6" s="10">
+      <c r="H6" s="22">
         <f>Inputs!G6</f>
         <v/>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="10">
+      <c r="A7" s="22">
         <f>Inputs!A7</f>
         <v/>
       </c>
-      <c r="B7" s="10">
+      <c r="B7" s="22">
         <f>Inputs!C7</f>
         <v/>
       </c>
-      <c r="C7" s="11">
+      <c r="C7" s="23">
         <f>Inputs!D7</f>
         <v/>
       </c>
-      <c r="D7" s="12">
+      <c r="D7" s="24">
         <f>Inputs!F7</f>
         <v/>
       </c>
-      <c r="E7" s="13">
+      <c r="E7" s="25">
         <f>C7*1000</f>
         <v/>
       </c>
-      <c r="F7" s="14">
+      <c r="F7" s="26">
         <f>E7*D7</f>
         <v/>
       </c>
-      <c r="G7" s="15">
+      <c r="G7" s="27">
         <f>F7/$F$21</f>
         <v/>
       </c>
-      <c r="H7" s="10">
+      <c r="H7" s="22">
         <f>Inputs!G7</f>
         <v/>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="10">
+      <c r="A8" s="22">
         <f>Inputs!A8</f>
         <v/>
       </c>
-      <c r="B8" s="10">
+      <c r="B8" s="22">
         <f>Inputs!C8</f>
         <v/>
       </c>
-      <c r="C8" s="11">
+      <c r="C8" s="23">
         <f>Inputs!D8</f>
         <v/>
       </c>
-      <c r="D8" s="12">
+      <c r="D8" s="24">
         <f>Inputs!F8</f>
         <v/>
       </c>
-      <c r="E8" s="13">
+      <c r="E8" s="25">
         <f>C8*1000</f>
         <v/>
       </c>
-      <c r="F8" s="14">
+      <c r="F8" s="26">
         <f>E8*D8</f>
         <v/>
       </c>
-      <c r="G8" s="15">
+      <c r="G8" s="27">
         <f>F8/$F$21</f>
         <v/>
       </c>
-      <c r="H8" s="10">
+      <c r="H8" s="22">
         <f>Inputs!G8</f>
         <v/>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="10">
+      <c r="A9" s="22">
         <f>Inputs!A9</f>
         <v/>
       </c>
-      <c r="B9" s="10">
+      <c r="B9" s="22">
         <f>Inputs!C9</f>
         <v/>
       </c>
-      <c r="C9" s="11">
+      <c r="C9" s="23">
         <f>Inputs!D9</f>
         <v/>
       </c>
-      <c r="D9" s="12">
+      <c r="D9" s="24">
         <f>Inputs!F9</f>
         <v/>
       </c>
-      <c r="E9" s="13">
+      <c r="E9" s="25">
         <f>C9*1000</f>
         <v/>
       </c>
-      <c r="F9" s="14">
+      <c r="F9" s="26">
         <f>E9*D9</f>
         <v/>
       </c>
-      <c r="G9" s="15">
+      <c r="G9" s="27">
         <f>F9/$F$21</f>
         <v/>
       </c>
-      <c r="H9" s="10">
+      <c r="H9" s="22">
         <f>Inputs!G9</f>
         <v/>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="10">
+      <c r="A10" s="22">
         <f>Inputs!A10</f>
         <v/>
       </c>
-      <c r="B10" s="10">
+      <c r="B10" s="22">
         <f>Inputs!C10</f>
         <v/>
       </c>
-      <c r="C10" s="11">
+      <c r="C10" s="23">
         <f>Inputs!D10</f>
         <v/>
       </c>
-      <c r="D10" s="12">
+      <c r="D10" s="24">
         <f>Inputs!F10</f>
         <v/>
       </c>
-      <c r="E10" s="13">
+      <c r="E10" s="25">
         <f>C10*1000</f>
         <v/>
       </c>
-      <c r="F10" s="14">
+      <c r="F10" s="26">
         <f>E10*D10</f>
         <v/>
       </c>
-      <c r="G10" s="15">
+      <c r="G10" s="27">
         <f>F10/$F$21</f>
         <v/>
       </c>
-      <c r="H10" s="10">
+      <c r="H10" s="22">
         <f>Inputs!G10</f>
         <v/>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="10">
+      <c r="A11" s="22">
         <f>Inputs!A11</f>
         <v/>
       </c>
-      <c r="B11" s="10">
+      <c r="B11" s="22">
         <f>Inputs!C11</f>
         <v/>
       </c>
-      <c r="C11" s="11">
+      <c r="C11" s="23">
         <f>Inputs!D11</f>
         <v/>
       </c>
-      <c r="D11" s="12">
+      <c r="D11" s="24">
         <f>Inputs!F11</f>
         <v/>
       </c>
-      <c r="E11" s="13">
+      <c r="E11" s="25">
         <f>C11*1000</f>
         <v/>
       </c>
-      <c r="F11" s="14">
+      <c r="F11" s="26">
         <f>E11*D11</f>
         <v/>
       </c>
-      <c r="G11" s="15">
+      <c r="G11" s="27">
         <f>F11/$F$21</f>
         <v/>
       </c>
-      <c r="H11" s="10">
+      <c r="H11" s="22">
         <f>Inputs!G11</f>
         <v/>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="10">
+      <c r="A12" s="22">
         <f>Inputs!A12</f>
         <v/>
       </c>
-      <c r="B12" s="10">
+      <c r="B12" s="22">
         <f>Inputs!C12</f>
         <v/>
       </c>
-      <c r="C12" s="11">
+      <c r="C12" s="23">
         <f>Inputs!D12</f>
         <v/>
       </c>
-      <c r="D12" s="12">
+      <c r="D12" s="24">
         <f>Inputs!F12</f>
         <v/>
       </c>
-      <c r="E12" s="13">
+      <c r="E12" s="25">
         <f>C12*1000</f>
         <v/>
       </c>
-      <c r="F12" s="14">
+      <c r="F12" s="26">
         <f>E12*D12</f>
         <v/>
       </c>
-      <c r="G12" s="15">
+      <c r="G12" s="27">
         <f>F12/$F$21</f>
         <v/>
       </c>
-      <c r="H12" s="10">
+      <c r="H12" s="22">
         <f>Inputs!G12</f>
         <v/>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="10">
+      <c r="A13" s="22">
         <f>Inputs!A13</f>
         <v/>
       </c>
-      <c r="B13" s="10">
+      <c r="B13" s="22">
         <f>Inputs!C13</f>
         <v/>
       </c>
-      <c r="C13" s="11">
+      <c r="C13" s="23">
         <f>Inputs!D13</f>
         <v/>
       </c>
-      <c r="D13" s="12">
+      <c r="D13" s="24">
         <f>Inputs!F13</f>
         <v/>
       </c>
-      <c r="E13" s="13">
+      <c r="E13" s="25">
         <f>C13*1000</f>
         <v/>
       </c>
-      <c r="F13" s="14">
+      <c r="F13" s="26">
         <f>E13*D13</f>
         <v/>
       </c>
-      <c r="G13" s="15">
+      <c r="G13" s="27">
         <f>F13/$F$21</f>
         <v/>
       </c>
-      <c r="H13" s="10">
+      <c r="H13" s="22">
         <f>Inputs!G13</f>
         <v/>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="10">
+      <c r="A14" s="22">
         <f>Inputs!A14</f>
         <v/>
       </c>
-      <c r="B14" s="10">
+      <c r="B14" s="22">
         <f>Inputs!C14</f>
         <v/>
       </c>
-      <c r="C14" s="11">
+      <c r="C14" s="23">
         <f>Inputs!D14</f>
         <v/>
       </c>
-      <c r="D14" s="12">
+      <c r="D14" s="24">
         <f>Inputs!F14</f>
         <v/>
       </c>
-      <c r="E14" s="13">
+      <c r="E14" s="25">
         <f>C14*1000</f>
         <v/>
       </c>
-      <c r="F14" s="14">
+      <c r="F14" s="26">
         <f>E14*D14</f>
         <v/>
       </c>
-      <c r="G14" s="15">
+      <c r="G14" s="27">
         <f>F14/$F$21</f>
         <v/>
       </c>
-      <c r="H14" s="10">
+      <c r="H14" s="22">
         <f>Inputs!G14</f>
         <v/>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="10">
+      <c r="A15" s="22">
         <f>Inputs!A15</f>
         <v/>
       </c>
-      <c r="B15" s="10">
+      <c r="B15" s="22">
         <f>Inputs!C15</f>
         <v/>
       </c>
-      <c r="C15" s="11">
+      <c r="C15" s="23">
         <f>Inputs!D15</f>
         <v/>
       </c>
-      <c r="D15" s="12">
+      <c r="D15" s="24">
         <f>Inputs!F15</f>
         <v/>
       </c>
-      <c r="E15" s="13">
+      <c r="E15" s="25">
         <f>C15*1000</f>
         <v/>
       </c>
-      <c r="F15" s="14">
+      <c r="F15" s="26">
         <f>E15*D15</f>
         <v/>
       </c>
-      <c r="G15" s="15">
+      <c r="G15" s="27">
         <f>F15/$F$21</f>
         <v/>
       </c>
-      <c r="H15" s="10">
+      <c r="H15" s="22">
         <f>Inputs!G15</f>
         <v/>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="10">
+      <c r="A16" s="22">
         <f>Inputs!A16</f>
         <v/>
       </c>
-      <c r="B16" s="10">
+      <c r="B16" s="22">
         <f>Inputs!C16</f>
         <v/>
       </c>
-      <c r="C16" s="11">
+      <c r="C16" s="23">
         <f>Inputs!D16</f>
         <v/>
       </c>
-      <c r="D16" s="12">
+      <c r="D16" s="24">
         <f>Inputs!F16</f>
         <v/>
       </c>
-      <c r="E16" s="13">
+      <c r="E16" s="25">
         <f>C16*1000</f>
         <v/>
       </c>
-      <c r="F16" s="14">
+      <c r="F16" s="26">
         <f>E16*D16</f>
         <v/>
       </c>
-      <c r="G16" s="15">
+      <c r="G16" s="27">
         <f>F16/$F$21</f>
         <v/>
       </c>
-      <c r="H16" s="10">
+      <c r="H16" s="22">
         <f>Inputs!G16</f>
         <v/>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="10">
+      <c r="A17" s="22">
         <f>Inputs!A17</f>
         <v/>
       </c>
-      <c r="B17" s="10">
+      <c r="B17" s="22">
         <f>Inputs!C17</f>
         <v/>
       </c>
-      <c r="C17" s="11">
+      <c r="C17" s="23">
         <f>Inputs!D17</f>
         <v/>
       </c>
-      <c r="D17" s="12">
+      <c r="D17" s="24">
         <f>Inputs!F17</f>
         <v/>
       </c>
-      <c r="E17" s="13">
+      <c r="E17" s="25">
         <f>C17*1000</f>
         <v/>
       </c>
-      <c r="F17" s="14">
+      <c r="F17" s="26">
         <f>E17*D17</f>
         <v/>
       </c>
-      <c r="G17" s="15">
+      <c r="G17" s="27">
         <f>F17/$F$21</f>
         <v/>
       </c>
-      <c r="H17" s="10">
+      <c r="H17" s="22">
         <f>Inputs!G17</f>
         <v/>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="10">
+      <c r="A18" s="22">
         <f>Inputs!A18</f>
         <v/>
       </c>
-      <c r="B18" s="10">
+      <c r="B18" s="22">
         <f>Inputs!C18</f>
         <v/>
       </c>
-      <c r="C18" s="11">
+      <c r="C18" s="23">
         <f>Inputs!D18</f>
         <v/>
       </c>
-      <c r="D18" s="12">
+      <c r="D18" s="24">
         <f>Inputs!F18</f>
         <v/>
       </c>
-      <c r="E18" s="13">
+      <c r="E18" s="25">
         <f>C18*1000</f>
         <v/>
       </c>
-      <c r="F18" s="14">
+      <c r="F18" s="26">
         <f>E18*D18</f>
         <v/>
       </c>
-      <c r="G18" s="15">
+      <c r="G18" s="27">
         <f>F18/$F$21</f>
         <v/>
       </c>
-      <c r="H18" s="10">
+      <c r="H18" s="22">
         <f>Inputs!G18</f>
         <v/>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="10">
+      <c r="A19" s="22">
         <f>Inputs!A19</f>
         <v/>
       </c>
-      <c r="B19" s="10">
+      <c r="B19" s="22">
         <f>Inputs!C19</f>
         <v/>
       </c>
-      <c r="C19" s="11">
+      <c r="C19" s="23">
         <f>Inputs!D19</f>
         <v/>
       </c>
-      <c r="D19" s="12">
+      <c r="D19" s="24">
         <f>Inputs!F19</f>
         <v/>
       </c>
-      <c r="E19" s="13">
+      <c r="E19" s="25">
         <f>C19*1000</f>
         <v/>
       </c>
-      <c r="F19" s="14">
+      <c r="F19" s="26">
         <f>E19*D19</f>
         <v/>
       </c>
-      <c r="G19" s="15">
+      <c r="G19" s="27">
         <f>F19/$F$21</f>
         <v/>
       </c>
-      <c r="H19" s="10">
+      <c r="H19" s="22">
         <f>Inputs!G19</f>
         <v/>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="10">
+      <c r="A20" s="22">
         <f>Inputs!A20</f>
         <v/>
       </c>
-      <c r="B20" s="10">
+      <c r="B20" s="22">
         <f>Inputs!C20</f>
         <v/>
       </c>
-      <c r="C20" s="11">
+      <c r="C20" s="23">
         <f>Inputs!D20</f>
         <v/>
       </c>
-      <c r="D20" s="12">
+      <c r="D20" s="24">
         <f>Inputs!F20</f>
         <v/>
       </c>
-      <c r="E20" s="13">
+      <c r="E20" s="25">
         <f>C20*1000</f>
         <v/>
       </c>
-      <c r="F20" s="14">
+      <c r="F20" s="26">
         <f>E20*D20</f>
         <v/>
       </c>
-      <c r="G20" s="15">
+      <c r="G20" s="27">
         <f>F20/$F$21</f>
         <v/>
       </c>
-      <c r="H20" s="10">
+      <c r="H20" s="22">
         <f>Inputs!G20</f>
         <v/>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="16" t="inlineStr">
+      <c r="A21" s="28" t="inlineStr">
         <is>
           <t>BASKET VALUE / TONNE REO  →</t>
         </is>
       </c>
-      <c r="F21" s="17">
+      <c r="F21" s="29">
         <f>SUM(F4:F20)</f>
         <v/>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="18" t="inlineStr">
+      <c r="A23" s="30" t="inlineStr">
         <is>
           <t>Memo headline — magnet elements (NdPr+Dy+Tb) share of basket value:</t>
         </is>
       </c>
-      <c r="F23" s="19">
+      <c r="F23" s="31">
         <f>SUMIF(H4:H20,"Yes",F4:F20)/$F$21</f>
         <v/>
       </c>
@@ -1957,7 +2453,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1994,549 +2490,549 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="18" t="inlineStr">
+      <c r="A3" s="30" t="inlineStr">
         <is>
           <t>Scenario assumptions (editable):</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="20" t="inlineStr">
+      <c r="A4" s="14" t="inlineStr">
         <is>
           <t>Floor — NdPr price multiplier</t>
         </is>
       </c>
-      <c r="B4" s="21" t="n">
+      <c r="B4" s="32" t="n">
         <v>1.25</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="20" t="inlineStr">
+      <c r="A5" s="14" t="inlineStr">
         <is>
           <t>Shock — heavy-RE price multiplier</t>
         </is>
       </c>
-      <c r="B5" s="21" t="n">
+      <c r="B5" s="32" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="20" t="inlineStr">
+      <c r="A6" s="14" t="inlineStr">
         <is>
           <t>Shock — NdPr price multiplier</t>
         </is>
       </c>
-      <c r="B6" s="21" t="n">
+      <c r="B6" s="32" t="n">
         <v>1.4</v>
       </c>
     </row>
     <row r="8" ht="36" customHeight="1">
-      <c r="A8" s="4" t="inlineStr">
+      <c r="A8" s="16" t="inlineStr">
         <is>
           <t>Element</t>
         </is>
       </c>
-      <c r="B8" s="4" t="inlineStr">
+      <c r="B8" s="16" t="inlineStr">
         <is>
           <t>Group</t>
         </is>
       </c>
-      <c r="C8" s="4" t="inlineStr">
+      <c r="C8" s="16" t="inlineStr">
         <is>
           <t>Base value
 USD/tonne</t>
         </is>
       </c>
-      <c r="D8" s="4" t="inlineStr">
+      <c r="D8" s="16" t="inlineStr">
         <is>
           <t>Floor scenario
 USD/tonne</t>
         </is>
       </c>
-      <c r="E8" s="4" t="inlineStr">
+      <c r="E8" s="16" t="inlineStr">
         <is>
           <t>Export-control shock
 USD/tonne</t>
         </is>
       </c>
-      <c r="F8" s="4" t="inlineStr">
+      <c r="F8" s="16" t="inlineStr">
         <is>
           <t>Magnet element?</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="10">
+      <c r="A9" s="22">
         <f>Calc!A4</f>
         <v/>
       </c>
-      <c r="B9" s="10">
+      <c r="B9" s="22">
         <f>Calc!B4</f>
         <v/>
       </c>
-      <c r="C9" s="14">
+      <c r="C9" s="33">
         <f>Calc!F4</f>
         <v/>
       </c>
-      <c r="D9" s="14">
+      <c r="D9" s="26">
         <f>Calc!F4*IF(OR(ISNUMBER(SEARCH("(Nd)",Calc!A4)),ISNUMBER(SEARCH("(Pr)",Calc!A4))),$B4,1)</f>
         <v/>
       </c>
-      <c r="E9" s="14">
+      <c r="E9" s="26">
         <f>Calc!F4*IF(OR(ISNUMBER(SEARCH("(Nd)",Calc!A4)),ISNUMBER(SEARCH("(Pr)",Calc!A4))),$B6,IF(ISNUMBER(SEARCH("Heavy",Calc!B4)),$B5,1))</f>
         <v/>
       </c>
-      <c r="F9" s="10">
+      <c r="F9" s="22">
         <f>Calc!H4</f>
         <v/>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="10">
+      <c r="A10" s="22">
         <f>Calc!A5</f>
         <v/>
       </c>
-      <c r="B10" s="10">
+      <c r="B10" s="22">
         <f>Calc!B5</f>
         <v/>
       </c>
-      <c r="C10" s="14">
+      <c r="C10" s="33">
         <f>Calc!F5</f>
         <v/>
       </c>
-      <c r="D10" s="14">
+      <c r="D10" s="26">
         <f>Calc!F5*IF(OR(ISNUMBER(SEARCH("(Nd)",Calc!A5)),ISNUMBER(SEARCH("(Pr)",Calc!A5))),$B4,1)</f>
         <v/>
       </c>
-      <c r="E10" s="14">
+      <c r="E10" s="26">
         <f>Calc!F5*IF(OR(ISNUMBER(SEARCH("(Nd)",Calc!A5)),ISNUMBER(SEARCH("(Pr)",Calc!A5))),$B6,IF(ISNUMBER(SEARCH("Heavy",Calc!B5)),$B5,1))</f>
         <v/>
       </c>
-      <c r="F10" s="10">
+      <c r="F10" s="22">
         <f>Calc!H5</f>
         <v/>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="10">
+      <c r="A11" s="22">
         <f>Calc!A6</f>
         <v/>
       </c>
-      <c r="B11" s="10">
+      <c r="B11" s="22">
         <f>Calc!B6</f>
         <v/>
       </c>
-      <c r="C11" s="14">
+      <c r="C11" s="33">
         <f>Calc!F6</f>
         <v/>
       </c>
-      <c r="D11" s="14">
+      <c r="D11" s="26">
         <f>Calc!F6*IF(OR(ISNUMBER(SEARCH("(Nd)",Calc!A6)),ISNUMBER(SEARCH("(Pr)",Calc!A6))),$B4,1)</f>
         <v/>
       </c>
-      <c r="E11" s="14">
+      <c r="E11" s="26">
         <f>Calc!F6*IF(OR(ISNUMBER(SEARCH("(Nd)",Calc!A6)),ISNUMBER(SEARCH("(Pr)",Calc!A6))),$B6,IF(ISNUMBER(SEARCH("Heavy",Calc!B6)),$B5,1))</f>
         <v/>
       </c>
-      <c r="F11" s="10">
+      <c r="F11" s="22">
         <f>Calc!H6</f>
         <v/>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="10">
+      <c r="A12" s="22">
         <f>Calc!A7</f>
         <v/>
       </c>
-      <c r="B12" s="10">
+      <c r="B12" s="22">
         <f>Calc!B7</f>
         <v/>
       </c>
-      <c r="C12" s="14">
+      <c r="C12" s="33">
         <f>Calc!F7</f>
         <v/>
       </c>
-      <c r="D12" s="14">
+      <c r="D12" s="26">
         <f>Calc!F7*IF(OR(ISNUMBER(SEARCH("(Nd)",Calc!A7)),ISNUMBER(SEARCH("(Pr)",Calc!A7))),$B4,1)</f>
         <v/>
       </c>
-      <c r="E12" s="14">
+      <c r="E12" s="26">
         <f>Calc!F7*IF(OR(ISNUMBER(SEARCH("(Nd)",Calc!A7)),ISNUMBER(SEARCH("(Pr)",Calc!A7))),$B6,IF(ISNUMBER(SEARCH("Heavy",Calc!B7)),$B5,1))</f>
         <v/>
       </c>
-      <c r="F12" s="10">
+      <c r="F12" s="22">
         <f>Calc!H7</f>
         <v/>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="10">
+      <c r="A13" s="22">
         <f>Calc!A8</f>
         <v/>
       </c>
-      <c r="B13" s="10">
+      <c r="B13" s="22">
         <f>Calc!B8</f>
         <v/>
       </c>
-      <c r="C13" s="14">
+      <c r="C13" s="33">
         <f>Calc!F8</f>
         <v/>
       </c>
-      <c r="D13" s="14">
+      <c r="D13" s="26">
         <f>Calc!F8*IF(OR(ISNUMBER(SEARCH("(Nd)",Calc!A8)),ISNUMBER(SEARCH("(Pr)",Calc!A8))),$B4,1)</f>
         <v/>
       </c>
-      <c r="E13" s="14">
+      <c r="E13" s="26">
         <f>Calc!F8*IF(OR(ISNUMBER(SEARCH("(Nd)",Calc!A8)),ISNUMBER(SEARCH("(Pr)",Calc!A8))),$B6,IF(ISNUMBER(SEARCH("Heavy",Calc!B8)),$B5,1))</f>
         <v/>
       </c>
-      <c r="F13" s="10">
+      <c r="F13" s="22">
         <f>Calc!H8</f>
         <v/>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="10">
+      <c r="A14" s="22">
         <f>Calc!A9</f>
         <v/>
       </c>
-      <c r="B14" s="10">
+      <c r="B14" s="22">
         <f>Calc!B9</f>
         <v/>
       </c>
-      <c r="C14" s="14">
+      <c r="C14" s="33">
         <f>Calc!F9</f>
         <v/>
       </c>
-      <c r="D14" s="14">
+      <c r="D14" s="26">
         <f>Calc!F9*IF(OR(ISNUMBER(SEARCH("(Nd)",Calc!A9)),ISNUMBER(SEARCH("(Pr)",Calc!A9))),$B4,1)</f>
         <v/>
       </c>
-      <c r="E14" s="14">
+      <c r="E14" s="26">
         <f>Calc!F9*IF(OR(ISNUMBER(SEARCH("(Nd)",Calc!A9)),ISNUMBER(SEARCH("(Pr)",Calc!A9))),$B6,IF(ISNUMBER(SEARCH("Heavy",Calc!B9)),$B5,1))</f>
         <v/>
       </c>
-      <c r="F14" s="10">
+      <c r="F14" s="22">
         <f>Calc!H9</f>
         <v/>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="10">
+      <c r="A15" s="22">
         <f>Calc!A10</f>
         <v/>
       </c>
-      <c r="B15" s="10">
+      <c r="B15" s="22">
         <f>Calc!B10</f>
         <v/>
       </c>
-      <c r="C15" s="14">
+      <c r="C15" s="33">
         <f>Calc!F10</f>
         <v/>
       </c>
-      <c r="D15" s="14">
+      <c r="D15" s="26">
         <f>Calc!F10*IF(OR(ISNUMBER(SEARCH("(Nd)",Calc!A10)),ISNUMBER(SEARCH("(Pr)",Calc!A10))),$B4,1)</f>
         <v/>
       </c>
-      <c r="E15" s="14">
+      <c r="E15" s="26">
         <f>Calc!F10*IF(OR(ISNUMBER(SEARCH("(Nd)",Calc!A10)),ISNUMBER(SEARCH("(Pr)",Calc!A10))),$B6,IF(ISNUMBER(SEARCH("Heavy",Calc!B10)),$B5,1))</f>
         <v/>
       </c>
-      <c r="F15" s="10">
+      <c r="F15" s="22">
         <f>Calc!H10</f>
         <v/>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="10">
+      <c r="A16" s="22">
         <f>Calc!A11</f>
         <v/>
       </c>
-      <c r="B16" s="10">
+      <c r="B16" s="22">
         <f>Calc!B11</f>
         <v/>
       </c>
-      <c r="C16" s="14">
+      <c r="C16" s="33">
         <f>Calc!F11</f>
         <v/>
       </c>
-      <c r="D16" s="14">
+      <c r="D16" s="26">
         <f>Calc!F11*IF(OR(ISNUMBER(SEARCH("(Nd)",Calc!A11)),ISNUMBER(SEARCH("(Pr)",Calc!A11))),$B4,1)</f>
         <v/>
       </c>
-      <c r="E16" s="14">
+      <c r="E16" s="26">
         <f>Calc!F11*IF(OR(ISNUMBER(SEARCH("(Nd)",Calc!A11)),ISNUMBER(SEARCH("(Pr)",Calc!A11))),$B6,IF(ISNUMBER(SEARCH("Heavy",Calc!B11)),$B5,1))</f>
         <v/>
       </c>
-      <c r="F16" s="10">
+      <c r="F16" s="22">
         <f>Calc!H11</f>
         <v/>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="10">
+      <c r="A17" s="22">
         <f>Calc!A12</f>
         <v/>
       </c>
-      <c r="B17" s="10">
+      <c r="B17" s="22">
         <f>Calc!B12</f>
         <v/>
       </c>
-      <c r="C17" s="14">
+      <c r="C17" s="33">
         <f>Calc!F12</f>
         <v/>
       </c>
-      <c r="D17" s="14">
+      <c r="D17" s="26">
         <f>Calc!F12*IF(OR(ISNUMBER(SEARCH("(Nd)",Calc!A12)),ISNUMBER(SEARCH("(Pr)",Calc!A12))),$B4,1)</f>
         <v/>
       </c>
-      <c r="E17" s="14">
+      <c r="E17" s="26">
         <f>Calc!F12*IF(OR(ISNUMBER(SEARCH("(Nd)",Calc!A12)),ISNUMBER(SEARCH("(Pr)",Calc!A12))),$B6,IF(ISNUMBER(SEARCH("Heavy",Calc!B12)),$B5,1))</f>
         <v/>
       </c>
-      <c r="F17" s="10">
+      <c r="F17" s="22">
         <f>Calc!H12</f>
         <v/>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="10">
+      <c r="A18" s="22">
         <f>Calc!A13</f>
         <v/>
       </c>
-      <c r="B18" s="10">
+      <c r="B18" s="22">
         <f>Calc!B13</f>
         <v/>
       </c>
-      <c r="C18" s="14">
+      <c r="C18" s="33">
         <f>Calc!F13</f>
         <v/>
       </c>
-      <c r="D18" s="14">
+      <c r="D18" s="26">
         <f>Calc!F13*IF(OR(ISNUMBER(SEARCH("(Nd)",Calc!A13)),ISNUMBER(SEARCH("(Pr)",Calc!A13))),$B4,1)</f>
         <v/>
       </c>
-      <c r="E18" s="14">
+      <c r="E18" s="26">
         <f>Calc!F13*IF(OR(ISNUMBER(SEARCH("(Nd)",Calc!A13)),ISNUMBER(SEARCH("(Pr)",Calc!A13))),$B6,IF(ISNUMBER(SEARCH("Heavy",Calc!B13)),$B5,1))</f>
         <v/>
       </c>
-      <c r="F18" s="10">
+      <c r="F18" s="22">
         <f>Calc!H13</f>
         <v/>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="10">
+      <c r="A19" s="22">
         <f>Calc!A14</f>
         <v/>
       </c>
-      <c r="B19" s="10">
+      <c r="B19" s="22">
         <f>Calc!B14</f>
         <v/>
       </c>
-      <c r="C19" s="14">
+      <c r="C19" s="33">
         <f>Calc!F14</f>
         <v/>
       </c>
-      <c r="D19" s="14">
+      <c r="D19" s="26">
         <f>Calc!F14*IF(OR(ISNUMBER(SEARCH("(Nd)",Calc!A14)),ISNUMBER(SEARCH("(Pr)",Calc!A14))),$B4,1)</f>
         <v/>
       </c>
-      <c r="E19" s="14">
+      <c r="E19" s="26">
         <f>Calc!F14*IF(OR(ISNUMBER(SEARCH("(Nd)",Calc!A14)),ISNUMBER(SEARCH("(Pr)",Calc!A14))),$B6,IF(ISNUMBER(SEARCH("Heavy",Calc!B14)),$B5,1))</f>
         <v/>
       </c>
-      <c r="F19" s="10">
+      <c r="F19" s="22">
         <f>Calc!H14</f>
         <v/>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="10">
+      <c r="A20" s="22">
         <f>Calc!A15</f>
         <v/>
       </c>
-      <c r="B20" s="10">
+      <c r="B20" s="22">
         <f>Calc!B15</f>
         <v/>
       </c>
-      <c r="C20" s="14">
+      <c r="C20" s="33">
         <f>Calc!F15</f>
         <v/>
       </c>
-      <c r="D20" s="14">
+      <c r="D20" s="26">
         <f>Calc!F15*IF(OR(ISNUMBER(SEARCH("(Nd)",Calc!A15)),ISNUMBER(SEARCH("(Pr)",Calc!A15))),$B4,1)</f>
         <v/>
       </c>
-      <c r="E20" s="14">
+      <c r="E20" s="26">
         <f>Calc!F15*IF(OR(ISNUMBER(SEARCH("(Nd)",Calc!A15)),ISNUMBER(SEARCH("(Pr)",Calc!A15))),$B6,IF(ISNUMBER(SEARCH("Heavy",Calc!B15)),$B5,1))</f>
         <v/>
       </c>
-      <c r="F20" s="10">
+      <c r="F20" s="22">
         <f>Calc!H15</f>
         <v/>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="10">
+      <c r="A21" s="22">
         <f>Calc!A16</f>
         <v/>
       </c>
-      <c r="B21" s="10">
+      <c r="B21" s="22">
         <f>Calc!B16</f>
         <v/>
       </c>
-      <c r="C21" s="14">
+      <c r="C21" s="33">
         <f>Calc!F16</f>
         <v/>
       </c>
-      <c r="D21" s="14">
+      <c r="D21" s="26">
         <f>Calc!F16*IF(OR(ISNUMBER(SEARCH("(Nd)",Calc!A16)),ISNUMBER(SEARCH("(Pr)",Calc!A16))),$B4,1)</f>
         <v/>
       </c>
-      <c r="E21" s="14">
+      <c r="E21" s="26">
         <f>Calc!F16*IF(OR(ISNUMBER(SEARCH("(Nd)",Calc!A16)),ISNUMBER(SEARCH("(Pr)",Calc!A16))),$B6,IF(ISNUMBER(SEARCH("Heavy",Calc!B16)),$B5,1))</f>
         <v/>
       </c>
-      <c r="F21" s="10">
+      <c r="F21" s="22">
         <f>Calc!H16</f>
         <v/>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="10">
+      <c r="A22" s="22">
         <f>Calc!A17</f>
         <v/>
       </c>
-      <c r="B22" s="10">
+      <c r="B22" s="22">
         <f>Calc!B17</f>
         <v/>
       </c>
-      <c r="C22" s="14">
+      <c r="C22" s="33">
         <f>Calc!F17</f>
         <v/>
       </c>
-      <c r="D22" s="14">
+      <c r="D22" s="26">
         <f>Calc!F17*IF(OR(ISNUMBER(SEARCH("(Nd)",Calc!A17)),ISNUMBER(SEARCH("(Pr)",Calc!A17))),$B4,1)</f>
         <v/>
       </c>
-      <c r="E22" s="14">
+      <c r="E22" s="26">
         <f>Calc!F17*IF(OR(ISNUMBER(SEARCH("(Nd)",Calc!A17)),ISNUMBER(SEARCH("(Pr)",Calc!A17))),$B6,IF(ISNUMBER(SEARCH("Heavy",Calc!B17)),$B5,1))</f>
         <v/>
       </c>
-      <c r="F22" s="10">
+      <c r="F22" s="22">
         <f>Calc!H17</f>
         <v/>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="10">
+      <c r="A23" s="22">
         <f>Calc!A18</f>
         <v/>
       </c>
-      <c r="B23" s="10">
+      <c r="B23" s="22">
         <f>Calc!B18</f>
         <v/>
       </c>
-      <c r="C23" s="14">
+      <c r="C23" s="33">
         <f>Calc!F18</f>
         <v/>
       </c>
-      <c r="D23" s="14">
+      <c r="D23" s="26">
         <f>Calc!F18*IF(OR(ISNUMBER(SEARCH("(Nd)",Calc!A18)),ISNUMBER(SEARCH("(Pr)",Calc!A18))),$B4,1)</f>
         <v/>
       </c>
-      <c r="E23" s="14">
+      <c r="E23" s="26">
         <f>Calc!F18*IF(OR(ISNUMBER(SEARCH("(Nd)",Calc!A18)),ISNUMBER(SEARCH("(Pr)",Calc!A18))),$B6,IF(ISNUMBER(SEARCH("Heavy",Calc!B18)),$B5,1))</f>
         <v/>
       </c>
-      <c r="F23" s="10">
+      <c r="F23" s="22">
         <f>Calc!H18</f>
         <v/>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="10">
+      <c r="A24" s="22">
         <f>Calc!A19</f>
         <v/>
       </c>
-      <c r="B24" s="10">
+      <c r="B24" s="22">
         <f>Calc!B19</f>
         <v/>
       </c>
-      <c r="C24" s="14">
+      <c r="C24" s="33">
         <f>Calc!F19</f>
         <v/>
       </c>
-      <c r="D24" s="14">
+      <c r="D24" s="26">
         <f>Calc!F19*IF(OR(ISNUMBER(SEARCH("(Nd)",Calc!A19)),ISNUMBER(SEARCH("(Pr)",Calc!A19))),$B4,1)</f>
         <v/>
       </c>
-      <c r="E24" s="14">
+      <c r="E24" s="26">
         <f>Calc!F19*IF(OR(ISNUMBER(SEARCH("(Nd)",Calc!A19)),ISNUMBER(SEARCH("(Pr)",Calc!A19))),$B6,IF(ISNUMBER(SEARCH("Heavy",Calc!B19)),$B5,1))</f>
         <v/>
       </c>
-      <c r="F24" s="10">
+      <c r="F24" s="22">
         <f>Calc!H19</f>
         <v/>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="10">
+      <c r="A25" s="22">
         <f>Calc!A20</f>
         <v/>
       </c>
-      <c r="B25" s="10">
+      <c r="B25" s="22">
         <f>Calc!B20</f>
         <v/>
       </c>
-      <c r="C25" s="14">
+      <c r="C25" s="33">
         <f>Calc!F20</f>
         <v/>
       </c>
-      <c r="D25" s="14">
+      <c r="D25" s="26">
         <f>Calc!F20*IF(OR(ISNUMBER(SEARCH("(Nd)",Calc!A20)),ISNUMBER(SEARCH("(Pr)",Calc!A20))),$B4,1)</f>
         <v/>
       </c>
-      <c r="E25" s="14">
+      <c r="E25" s="26">
         <f>Calc!F20*IF(OR(ISNUMBER(SEARCH("(Nd)",Calc!A20)),ISNUMBER(SEARCH("(Pr)",Calc!A20))),$B6,IF(ISNUMBER(SEARCH("Heavy",Calc!B20)),$B5,1))</f>
         <v/>
       </c>
-      <c r="F25" s="10">
+      <c r="F25" s="22">
         <f>Calc!H20</f>
         <v/>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="22" t="inlineStr">
+      <c r="A26" s="34" t="inlineStr">
         <is>
           <t>BASKET VALUE / TONNE  →</t>
         </is>
       </c>
-      <c r="C26" s="17">
+      <c r="C26" s="29">
         <f>SUM(C9:C25)</f>
         <v/>
       </c>
-      <c r="D26" s="17">
+      <c r="D26" s="29">
         <f>SUM(D9:D25)</f>
         <v/>
       </c>
-      <c r="E26" s="17">
+      <c r="E26" s="29">
         <f>SUM(E9:E25)</f>
         <v/>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="23" t="inlineStr">
+      <c r="A27" s="35" t="inlineStr">
         <is>
           <t>Uplift vs base</t>
         </is>
       </c>
-      <c r="D27" s="24">
+      <c r="D27" s="36">
         <f>D26/C26-1</f>
         <v/>
       </c>
-      <c r="E27" s="24">
+      <c r="E27" s="36">
         <f>E26/C26-1</f>
         <v/>
       </c>
@@ -2550,7 +3046,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2580,12 +3076,12 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="25" t="inlineStr">
+      <c r="A3" s="13" t="inlineStr">
         <is>
           <t>Element</t>
         </is>
       </c>
-      <c r="B3" s="25" t="inlineStr">
+      <c r="B3" s="13" t="inlineStr">
         <is>
           <t>% of basket value</t>
         </is>
@@ -2596,7 +3092,7 @@
         <f>Calc!A4</f>
         <v/>
       </c>
-      <c r="B4" s="26">
+      <c r="B4" s="37">
         <f>Calc!G4</f>
         <v/>
       </c>
@@ -2606,7 +3102,7 @@
         <f>Calc!A5</f>
         <v/>
       </c>
-      <c r="B5" s="26">
+      <c r="B5" s="37">
         <f>Calc!G5</f>
         <v/>
       </c>
@@ -2616,7 +3112,7 @@
         <f>Calc!A6</f>
         <v/>
       </c>
-      <c r="B6" s="26">
+      <c r="B6" s="37">
         <f>Calc!G6</f>
         <v/>
       </c>
@@ -2626,7 +3122,7 @@
         <f>Calc!A7</f>
         <v/>
       </c>
-      <c r="B7" s="26">
+      <c r="B7" s="37">
         <f>Calc!G7</f>
         <v/>
       </c>
@@ -2636,7 +3132,7 @@
         <f>Calc!A8</f>
         <v/>
       </c>
-      <c r="B8" s="26">
+      <c r="B8" s="37">
         <f>Calc!G8</f>
         <v/>
       </c>
@@ -2646,7 +3142,7 @@
         <f>Calc!A9</f>
         <v/>
       </c>
-      <c r="B9" s="26">
+      <c r="B9" s="37">
         <f>Calc!G9</f>
         <v/>
       </c>
@@ -2656,7 +3152,7 @@
         <f>Calc!A10</f>
         <v/>
       </c>
-      <c r="B10" s="26">
+      <c r="B10" s="37">
         <f>Calc!G10</f>
         <v/>
       </c>
@@ -2666,7 +3162,7 @@
         <f>Calc!A11</f>
         <v/>
       </c>
-      <c r="B11" s="26">
+      <c r="B11" s="37">
         <f>Calc!G11</f>
         <v/>
       </c>
@@ -2676,7 +3172,7 @@
         <f>Calc!A12</f>
         <v/>
       </c>
-      <c r="B12" s="26">
+      <c r="B12" s="37">
         <f>Calc!G12</f>
         <v/>
       </c>
@@ -2686,7 +3182,7 @@
         <f>Calc!A13</f>
         <v/>
       </c>
-      <c r="B13" s="26">
+      <c r="B13" s="37">
         <f>Calc!G13</f>
         <v/>
       </c>
@@ -2696,7 +3192,7 @@
         <f>Calc!A14</f>
         <v/>
       </c>
-      <c r="B14" s="26">
+      <c r="B14" s="37">
         <f>Calc!G14</f>
         <v/>
       </c>
@@ -2706,7 +3202,7 @@
         <f>Calc!A15</f>
         <v/>
       </c>
-      <c r="B15" s="26">
+      <c r="B15" s="37">
         <f>Calc!G15</f>
         <v/>
       </c>
@@ -2716,7 +3212,7 @@
         <f>Calc!A16</f>
         <v/>
       </c>
-      <c r="B16" s="26">
+      <c r="B16" s="37">
         <f>Calc!G16</f>
         <v/>
       </c>
@@ -2726,7 +3222,7 @@
         <f>Calc!A17</f>
         <v/>
       </c>
-      <c r="B17" s="26">
+      <c r="B17" s="37">
         <f>Calc!G17</f>
         <v/>
       </c>
@@ -2736,7 +3232,7 @@
         <f>Calc!A18</f>
         <v/>
       </c>
-      <c r="B18" s="26">
+      <c r="B18" s="37">
         <f>Calc!G18</f>
         <v/>
       </c>
@@ -2746,7 +3242,7 @@
         <f>Calc!A19</f>
         <v/>
       </c>
-      <c r="B19" s="26">
+      <c r="B19" s="37">
         <f>Calc!G19</f>
         <v/>
       </c>
@@ -2756,7 +3252,7 @@
         <f>Calc!A20</f>
         <v/>
       </c>
-      <c r="B20" s="26">
+      <c r="B20" s="37">
         <f>Calc!G20</f>
         <v/>
       </c>
@@ -2771,13 +3267,13 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A20"/>
+  <dimension ref="A1:A26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2794,7 +3290,7 @@
       <c r="A3" s="3" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="27" t="inlineStr">
+      <c r="A4" s="38" t="inlineStr">
         <is>
           <t>ALL NUMBERS IN THIS WORKBOOK ARE ILLUSTRATIVE PLACEHOLDERS.</t>
         </is>
@@ -2818,28 +3314,28 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="28" t="inlineStr">
+      <c r="A8" s="39" t="inlineStr">
         <is>
           <t xml:space="preserve">  1. Inputs!D (Example Deposit A) — [[INPUT]] real % by oxide for your deposit; rename the column to the deposit name.</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="28" t="inlineStr">
+      <c r="A9" s="39" t="inlineStr">
         <is>
           <t xml:space="preserve">  2. Inputs!E (Example Deposit B) — [[INPUT]] a second real deposit, or delete the column.</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="28" t="inlineStr">
+      <c r="A10" s="39" t="inlineStr">
         <is>
           <t xml:space="preserve">  3. Inputs!F (Oxide price) — [[VERIFY]] live oxide prices (USD/kg) with an as-of date; note China-domestic vs ex-China/CIF (memo §1.5).</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="28" t="inlineStr">
+      <c r="A11" s="39" t="inlineStr">
         <is>
           <t xml:space="preserve">  4. Sensitivity!B4:B6 — [[MY VIEW]] your own floor / shock multipliers.</t>
         </is>
@@ -2868,27 +3364,65 @@
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
         <is>
+          <t>Color conventions (Street standard):</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  BLUE text = hardcoded input (yours to change; amber fill = must fill in).</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  BLACK text = formula within the tab. Do not overwrite.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  GREEN text = link pulling from another tab. Do not overwrite.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Double-underlined rows = final outputs (basket value / tonne).</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="3" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="3" t="inlineStr">
+        <is>
           <t>Headline number to quote in the memo: Calc!F&lt;total row&gt; (BASKET VALUE / TONNE REO). It is illustrative until step 1–3 are done.</t>
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="3" t="inlineStr"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="3" t="inlineStr">
+    <row r="23">
+      <c r="A23" s="3" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="3" t="inlineStr">
         <is>
           <t>Pricing caveat (mirror of memo §1.5 / Sources): rare-earth pricing is opaque, thin, two-regime, and goes stale fast. Date every price.</t>
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="3" t="inlineStr"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="3" t="inlineStr">
-        <is>
-          <t>Workbook generated by scripts/build_model.py on 2026-06-23.</t>
+    <row r="25">
+      <c r="A25" s="3" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="3" t="inlineStr">
+        <is>
+          <t>Workbook generated by scripts/build_model.py on 2026-07-07.</t>
         </is>
       </c>
     </row>
